--- a/tests/testdata/excel/フォルダ/スペース あり/スペースフォルダ内.xlsx
+++ b/tests/testdata/excel/フォルダ/スペース あり/スペースフォルダ内.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E8BF3A1-7DC6-4F86-A16B-314ED7B5A8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08864D9A-74E8-431F-BCFE-B6219421D133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{C68119A7-E6AF-433B-9F82-C08E95B86EF6}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{30A062C7-046D-48DB-A7AD-3F1399CDF5E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9132BB56-26E3-4E65-B24C-10C24E30AE6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE206025-DDB4-4CC4-AAD8-D4FD70F3A806}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/フォルダ/スペース あり/スペースフォルダ内.xlsx
+++ b/tests/testdata/excel/フォルダ/スペース あり/スペースフォルダ内.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08864D9A-74E8-431F-BCFE-B6219421D133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F788458F-D276-4562-BBF1-96025C8C6F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{30A062C7-046D-48DB-A7AD-3F1399CDF5E2}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{30CD7BF4-F78D-4751-A487-6A19F45E314C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE206025-DDB4-4CC4-AAD8-D4FD70F3A806}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15FAD20-4FFD-4D6B-A2BA-C916D38ABD22}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
